--- a/словари/преступность.xlsx
+++ b/словари/преступность.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF27D55-C68C-4A23-882F-171BD1B45E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD9F38D-2B08-4482-8A23-66CAC01470A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
   <si>
     <t>форма таких «рецензий» иногда немного напрягала</t>
   </si>
@@ -422,6 +422,18 @@
   </si>
   <si>
     <t>Гeны Шрaмa</t>
+  </si>
+  <si>
+    <t>отправился на Истринское водохранилище в пансионат</t>
+  </si>
+  <si>
+    <t>отправился на Истринское водо-хранилище в здравницу</t>
+  </si>
+  <si>
+    <t>назначивший обидчикам рандеву</t>
+  </si>
+  <si>
+    <t>назначивший обидчикам стрелку</t>
   </si>
 </sst>
 </file>
@@ -689,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="58.08984375" customWidth="1"/>
@@ -928,6 +940,14 @@
         <v>56</v>
       </c>
     </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -936,7 +956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="82.26953125" customWidth="1"/>
@@ -1021,6 +1041,14 @@
       </c>
       <c r="B10" s="2" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/словари/преступность.xlsx
+++ b/словари/преступность.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD9F38D-2B08-4482-8A23-66CAC01470A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FA4C6B-2BCB-4CB2-89BB-F6DDDDB16EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="неизменные_короткие" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>форма таких «рецензий» иногда немного напрягала</t>
   </si>
@@ -434,6 +434,18 @@
   </si>
   <si>
     <t>назначивший обидчикам стрелку</t>
+  </si>
+  <si>
+    <t>ту самую страшную цветную фотографию</t>
+  </si>
+  <si>
+    <t>тот самый страшный цветной снимок</t>
+  </si>
+  <si>
+    <t>Такая сумма мне и во сне не снилась</t>
+  </si>
+  <si>
+    <t>Такое количество денег мне и во сне не снилось</t>
   </si>
 </sst>
 </file>
@@ -701,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="58.08984375" customWidth="1"/>
@@ -946,6 +958,22 @@
       </c>
       <c r="B30" s="3" t="s">
         <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/словари/преступность.xlsx
+++ b/словари/преступность.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FA4C6B-2BCB-4CB2-89BB-F6DDDDB16EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50713564-6367-494A-B723-3444201E08F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="неизменные_короткие" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t>форма таких «рецензий» иногда немного напрягала</t>
   </si>
@@ -446,6 +446,96 @@
   </si>
   <si>
     <t>Такое количество денег мне и во сне не снилось</t>
+  </si>
+  <si>
+    <t>отвоевала для себя неплохие возможности</t>
+  </si>
+  <si>
+    <t>отвоевала для себя неплохие владения</t>
+  </si>
+  <si>
+    <t>«профессиональными» интересами</t>
+  </si>
+  <si>
+    <t>«искуссными» разделами</t>
+  </si>
+  <si>
+    <t>Интересы друзей</t>
+  </si>
+  <si>
+    <t>Цели друзей</t>
+  </si>
+  <si>
+    <t>мобильная долгопрудненская группировка. В основном в нее</t>
+  </si>
+  <si>
+    <t>незамедлительное долгопрудненское преступное сообщество В основном в него</t>
+  </si>
+  <si>
+    <t>какотипичном</t>
+  </si>
+  <si>
+    <t>как о типичном</t>
+  </si>
+  <si>
+    <t>Лабоцкого собственную команду</t>
+  </si>
+  <si>
+    <t>Лабоцкого собственное преступное сообщество</t>
+  </si>
+  <si>
+    <t>Было даже разоблачено грузинское преступное сообщество, поставившее</t>
+  </si>
+  <si>
+    <t>Была даже разоблачена грузинская преступная группировка, поставившая</t>
+  </si>
+  <si>
+    <t>одно из преступных сообществ решило</t>
+  </si>
+  <si>
+    <t>одна из банд на востоке города решила</t>
+  </si>
+  <si>
+    <t>замашки первогодка</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>другая версия. По ней</t>
+  </si>
+  <si>
+    <t>другой домысел. По нему</t>
+  </si>
+  <si>
+    <t>приносятхотя</t>
+  </si>
+  <si>
+    <t>приносят хотя</t>
+  </si>
+  <si>
+    <t>грузинская или казанская группировка, каждая из которых имела</t>
+  </si>
+  <si>
+    <t>грузинское или казанское преступное сообщество, каждое из которых имело</t>
+  </si>
+  <si>
+    <t>Старейшей в Москве считается измайловско-гольяновская группировка</t>
+  </si>
+  <si>
+    <t>Старейшим в Москве считается измайловско-гольяновское преступное сообщество</t>
+  </si>
+  <si>
+    <t>Подольская группировка насчитывает около 500 членов и считается самой крупной</t>
+  </si>
+  <si>
+    <t>Подольское преступное сообщество насчитывает около 500 членов и считается самым крупным</t>
+  </si>
+  <si>
+    <t>Группировка разделилась сначала на ореховскую и солнцевскую, а затем стала</t>
+  </si>
+  <si>
+    <t>Преступное сообщество разделилось сначала на ореховскую и солнцевскую, а затем стало</t>
   </si>
 </sst>
 </file>
@@ -508,7 +598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -520,6 +610,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -713,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="58.08984375" customWidth="1"/>
@@ -976,6 +1076,46 @@
         <v>124</v>
       </c>
     </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -984,66 +1124,66 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="82.26953125" customWidth="1"/>
-    <col min="2" max="2" width="79.54296875" customWidth="1"/>
+    <col min="1" max="1" width="59.90625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="79.54296875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" ht="29">
+      <c r="A3" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="A4" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="A5" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="A6" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="7" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1059,7 +1199,7 @@
       <c r="A9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1075,8 +1215,64 @@
       <c r="A11" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="7" t="s">
         <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="29">
+      <c r="A16" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="29">
+      <c r="A17" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29">
+      <c r="A18" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -1142,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="50.54296875" customWidth="1"/>
@@ -1266,6 +1462,30 @@
         <v>115</v>
       </c>
     </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/словари/преступность.xlsx
+++ b/словари/преступность.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50713564-6367-494A-B723-3444201E08F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9C9553-4828-4912-89EA-2B858B5BD9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="неизменные_короткие" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t>форма таких «рецензий» иногда немного напрягала</t>
   </si>
@@ -466,12 +466,6 @@
     <t>Цели друзей</t>
   </si>
   <si>
-    <t>мобильная долгопрудненская группировка. В основном в нее</t>
-  </si>
-  <si>
-    <t>незамедлительное долгопрудненское преступное сообщество В основном в него</t>
-  </si>
-  <si>
     <t>какотипичном</t>
   </si>
   <si>
@@ -536,6 +530,96 @@
   </si>
   <si>
     <t>Преступное сообщество разделилось сначала на ореховскую и солнцевскую, а затем стало</t>
+  </si>
+  <si>
+    <t>банда вымогателей, без нанесения ущерба жертвам похищения, была обезврежена</t>
+  </si>
+  <si>
+    <t>преступное сообщество вымогателей, без нанесения ущерба жертвам похищения, было обезврежено</t>
+  </si>
+  <si>
+    <t>главном направлением</t>
+  </si>
+  <si>
+    <t>главным направлением</t>
+  </si>
+  <si>
+    <t>оригиналы вывесили</t>
+  </si>
+  <si>
+    <t>маргиналы вывесили</t>
+  </si>
+  <si>
+    <t>спросил у Мираба домашний телефон</t>
+  </si>
+  <si>
+    <t>спросил у Мираба домаший числитель трубки связи</t>
+  </si>
+  <si>
+    <t>имел незаконченное среднее.</t>
+  </si>
+  <si>
+    <t>имел незаконченное среднее образование</t>
+  </si>
+  <si>
+    <t>.(Очкарик родился в лагере, первый срок за разбой получил в одиннадцать лет, а в общей сложности провел за колючкой четверть века.)</t>
+  </si>
+  <si>
+    <t>.Очкарик родился в лагере, первый срок за разбой получил в одиннадцать лет, а в общей сложности провел за колючкой четверть века.</t>
+  </si>
+  <si>
+    <t>на один и тот же магазин</t>
+  </si>
+  <si>
+    <t>на одну и ту же торговую точку</t>
+  </si>
+  <si>
+    <t>пристреливаетжертву</t>
+  </si>
+  <si>
+    <t>пристреливает жертву</t>
+  </si>
+  <si>
+    <t>оказалась пророческой. В тот день</t>
+  </si>
+  <si>
+    <t>оказалась пророческим. В тот день</t>
+  </si>
+  <si>
+    <t>Первая банда, которую старожилы МУРа сравнивали с «Черной кошкой», была разгромлена</t>
+  </si>
+  <si>
+    <t>Первое преступное сообщество, которое старожилы МУРа сравнивали с «Черной кошкой», было разгромлено</t>
+  </si>
+  <si>
+    <t>мощная и мобильная долгопрудненская группировка. В основном в нее</t>
+  </si>
+  <si>
+    <t>мощное и незамедлительное долгопрудненское преступное сообщество. В основном в него</t>
+  </si>
+  <si>
+    <t>а потом думал и</t>
+  </si>
+  <si>
+    <t>а потом думали</t>
+  </si>
+  <si>
+    <t>? – тесть жертвы</t>
+  </si>
+  <si>
+    <t>Т. – тесть жертвы</t>
+  </si>
+  <si>
+    <t>производитэкспроприацию</t>
+  </si>
+  <si>
+    <t>производит экспроприацию</t>
+  </si>
+  <si>
+    <t>Сакман</t>
+  </si>
+  <si>
+    <t>Самая</t>
   </si>
 </sst>
 </file>
@@ -813,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="58.08984375" customWidth="1"/>
@@ -1102,18 +1186,42 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -1124,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="59.90625" style="7" customWidth="1"/>
@@ -1219,59 +1327,67 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" ht="28.5">
       <c r="A12" s="2" t="s">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="29">
       <c r="A16" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="29">
       <c r="A17" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="29">
       <c r="A18" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="29">
+      <c r="A19" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B19" s="7" t="s">
         <v>154</v>
       </c>
     </row>
@@ -1283,7 +1399,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="137.453125" customWidth="1"/>
@@ -1330,6 +1446,14 @@
         <v>86</v>
       </c>
     </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" t="s">
+        <v>172</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1338,20 +1462,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="50.54296875" customWidth="1"/>
+    <col min="1" max="1" width="91.7265625" style="7" customWidth="1"/>
     <col min="2" max="2" width="49.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="7" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2" s="7" t="s">
         <v>88</v>
       </c>
       <c r="B2" t="s">
@@ -1359,7 +1483,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="A3" s="7" t="s">
         <v>90</v>
       </c>
       <c r="B3" t="s">
@@ -1367,7 +1491,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="A4" s="7" t="s">
         <v>92</v>
       </c>
       <c r="B4" t="s">
@@ -1375,7 +1499,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="A5" s="7" t="s">
         <v>94</v>
       </c>
       <c r="B5" t="s">
@@ -1383,7 +1507,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="A6" s="7" t="s">
         <v>96</v>
       </c>
       <c r="B6" t="s">
@@ -1391,7 +1515,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" t="s">
+      <c r="A7" s="7" t="s">
         <v>98</v>
       </c>
       <c r="B7" t="s">
@@ -1399,7 +1523,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="6" t="s">
         <v>100</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1431,7 +1555,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="6" t="s">
         <v>108</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1447,7 +1571,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="6" t="s">
         <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -1463,27 +1587,99 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="3" t="s">
-        <v>133</v>
+      <c r="A16" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="3" t="s">
-        <v>145</v>
+      <c r="A18" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="26.5">
+      <c r="A22" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B24" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B25" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/словари/преступность.xlsx
+++ b/словари/преступность.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9C9553-4828-4912-89EA-2B858B5BD9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFAEDD7-AD3B-4106-A79F-345080CB39F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="неизменные_короткие" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
   <si>
     <t>форма таких «рецензий» иногда немного напрягала</t>
   </si>
@@ -620,6 +620,18 @@
   </si>
   <si>
     <t>Самая</t>
+  </si>
+  <si>
+    <t>нереавизуемой</t>
+  </si>
+  <si>
+    <t>нереализуемой</t>
+  </si>
+  <si>
+    <t>уголовнотеррористического</t>
+  </si>
+  <si>
+    <t>уголовно-террористического</t>
   </si>
 </sst>
 </file>
@@ -1462,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="91.7265625" style="7" customWidth="1"/>
@@ -1682,6 +1694,22 @@
         <v>182</v>
       </c>
     </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B29" t="s">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
